--- a/AI云业务/客户结算/亿点云业务消耗费用.xlsx
+++ b/AI云业务/客户结算/亿点云业务消耗费用.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="腾讯云" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿里云" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="腾讯云" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="阿里云" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Akamai" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -521,32 +522,37 @@
           <t>账号信息</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>实际消耗（￥）</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>币种</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>实际消耗（原币）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>服务费比例</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>服务费金额（￥）</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>结算总金额（￥）</t>
+          <t>服务费金额（原币）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>结算总金额（原币）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>服务费是否支付</t>
         </is>
@@ -568,26 +574,31 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>261594.76</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>5231.9</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>266826.66</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -605,28 +616,33 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>531345.47</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>531345.47</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -644,26 +660,31 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>281692.01</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>5633.84</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>287325.85</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -681,28 +702,33 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>430155.4</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>430155.4</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -720,28 +746,33 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>468565.52</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>468565.52</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -759,47 +790,165 @@
           <t>亿点宇宙（陕西）信息科技有限公司</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>282543.41</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>5650.87</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>288194.28</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Akamai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Adnov</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>34982</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>34982</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Linode Invoice #32686932 · 币种 USD · 未换汇；票见 AI云业务/Akamai对账/亿点/2026-09/发票/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Akamai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AceMedia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53600.67</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>53600.67</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Linode Invoice #32686573 · 币种 USD · 未换汇；票见 AI云业务/Akamai对账/亿点/2026-09/发票/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>合计（人民币云）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="E11" s="7" t="n">
         <v>2255896.57</v>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="n">
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="7" t="n">
         <v>16516.61</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="H11" s="7" t="n">
         <v>2272413.18</v>
       </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>不含 Akamai（USD）</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>合计（Akamai·USD）</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88582.67</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>88582.67</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Adnov+AceMedia；勿与人民币合计相加</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -812,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -848,19 +997,24 @@
           <t>云厂商</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>实际消耗（￥）</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>币种</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>服务费金额（￥）</t>
+          <t>实际消耗（原币）</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>结算总金额（￥）</t>
+          <t>服务费金额（原币）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>结算总金额（原币）</t>
         </is>
       </c>
     </row>
@@ -875,13 +1029,18 @@
           <t>腾讯云</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>261594.76</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="E5" s="10" t="n">
         <v>5231.9</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="F5" s="10" t="n">
         <v>266826.66</v>
       </c>
     </row>
@@ -896,13 +1055,18 @@
           <t>阿里云</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>531345.47</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>531345.47</v>
       </c>
     </row>
@@ -917,13 +1081,18 @@
           <t>腾讯云</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>281692.01</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="E7" s="10" t="n">
         <v>5633.84</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="F7" s="10" t="n">
         <v>287325.85</v>
       </c>
     </row>
@@ -938,13 +1107,18 @@
           <t>阿里云</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>430155.4</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="F8" s="10" t="n">
         <v>430155.4</v>
       </c>
     </row>
@@ -959,13 +1133,18 @@
           <t>阿里云</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>468565.52</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="F9" s="10" t="n">
         <v>468565.52</v>
       </c>
     </row>
@@ -980,108 +1159,155 @@
           <t>腾讯云</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
         <v>282543.41</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="E10" s="10" t="n">
         <v>5650.87</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="F10" s="10" t="n">
         <v>288194.28</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Akamai（USD）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>88582.67</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>88582.67</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>二、每月总消耗（全云合计）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>业务所属期</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>实际消耗合计（￥）</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>服务费合计（￥）</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>结算合计（￥）</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>202607</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>792940.23</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>5231.9</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>798172.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>792940.23</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>5231.9</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>798172.13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>202608</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B16" s="7" t="n">
         <v>711847.41</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="D16" s="11" t="n">
         <v>5633.84</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="E16" s="11" t="n">
         <v>717481.25</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>202609</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>751108.9300000001</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D17" t="n">
         <v>5650.87</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E17" t="n">
         <v>756759.8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>全部期间合计</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B18" s="7" t="n">
         <v>2255896.57</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="D18" s="7" t="n">
         <v>16516.61</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>2272413.18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>说明：按月×云中 Akamai（USD）为美元原文，未换汇；「二、每月总消耗」仅含腾讯/阿里人民币。</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>88582.67</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>88582.67</v>
       </c>
     </row>
   </sheetData>
@@ -1401,4 +1627,117 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Akamai / Linode（金额 USD）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>业务所属期</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>账号信息</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>实际消耗（USD）</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Invoice No.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adnov</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>34982</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>32686932</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>票：20261001_USD34982.00_Invoice-32686932_Adnov.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AceMedia</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>53600.67</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>32686573</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>票：20261001_USD53600.67_Invoice-32686573_AceMedia.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>88582.67</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>币种 USD；未换汇</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>